--- a/stacked_model/results/validation/validation_per_fold_comparison.xlsx
+++ b/stacked_model/results/validation/validation_per_fold_comparison.xlsx
@@ -585,65 +585,65 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.518063526065347</v>
+        <v>4.085425153958832</v>
       </c>
       <c r="C2" t="n">
-        <v>2.96075856646099</v>
+        <v>3.268146302051433</v>
       </c>
       <c r="D2" t="n">
-        <v>2.795382267260514</v>
+        <v>3.247811934055953</v>
       </c>
       <c r="E2" t="n">
-        <v>2.742521004510899</v>
+        <v>3.052978924472381</v>
       </c>
       <c r="F2" t="n">
-        <v>2.193077675242523</v>
+        <v>2.322583668542769</v>
       </c>
       <c r="G2" t="n">
-        <v>2.028276421337497</v>
+        <v>2.467534444847869</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9437325474627397</v>
+        <v>0.9034803237873646</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9601474708877838</v>
+        <v>0.938234733559231</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9644751452920067</v>
+        <v>0.9390009479600042</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="N2" t="n">
-        <v>2.807324012912636</v>
+        <v>2.8045953856371</v>
       </c>
       <c r="O2" t="n">
-        <v>2.572204068296203</v>
+        <v>2.675898075508693</v>
       </c>
       <c r="P2" t="n">
-        <v>2.569783335524105</v>
+        <v>2.652961293267559</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>raw</t>
@@ -656,32 +656,32 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>0.5573049596043571</v>
+        <v>0.8172788519073992</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7226812588048328</v>
+        <v>0.8376132199028792</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5494433292683762</v>
+        <v>0.7303952559296119</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7142445831734023</v>
+        <v>0.585444479624512</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01641492342504414</v>
+        <v>0.03475440977186639</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02074259782926702</v>
+        <v>0.03552062417263957</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2351199446164327</v>
+        <v>0.1286973101284068</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2375406773885307</v>
+        <v>0.151634092369541</v>
       </c>
     </row>
     <row r="3">
@@ -689,65 +689,65 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>6.44807922878431</v>
+        <v>6.439259459759481</v>
       </c>
       <c r="C3" t="n">
-        <v>3.474600541257001</v>
+        <v>3.406973862946889</v>
       </c>
       <c r="D3" t="n">
-        <v>4.10302822191091</v>
+        <v>4.209590760365135</v>
       </c>
       <c r="E3" t="n">
-        <v>4.071162140565989</v>
+        <v>4.146151995286964</v>
       </c>
       <c r="F3" t="n">
-        <v>2.689500475763583</v>
+        <v>2.464117942584968</v>
       </c>
       <c r="G3" t="n">
-        <v>3.089717911460483</v>
+        <v>3.187896029899177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7817468597384037</v>
+        <v>0.7891475536494751</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9366262309436449</v>
+        <v>0.9409738579695258</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9116292014757369</v>
+        <v>0.9098871864111856</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="L3" t="n">
         <v>0.8421052631578947</v>
       </c>
       <c r="M3" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="N3" t="n">
-        <v>3.768527041718815</v>
+        <v>3.487448126730663</v>
       </c>
       <c r="O3" t="n">
-        <v>2.730466366266718</v>
+        <v>2.844132783669072</v>
       </c>
       <c r="P3" t="n">
-        <v>2.99203941215106</v>
+        <v>3.258027001628874</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>raw</t>
@@ -760,32 +760,32 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>2.973478687527308</v>
+        <v>3.032285596812592</v>
       </c>
       <c r="X3" t="n">
-        <v>2.345051006873399</v>
+        <v>2.229668699394346</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.381661664802406</v>
+        <v>1.682034052701995</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9814442291055063</v>
+        <v>0.9582559653877865</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1548793712052412</v>
+        <v>0.1518263043200507</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1298823417373332</v>
+        <v>0.1207396327617105</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.038060675452097</v>
+        <v>0.643315343061591</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7764876295677547</v>
+        <v>0.2294211251017888</v>
       </c>
     </row>
     <row r="4">
@@ -793,65 +793,65 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>6.432438756008418</v>
+        <v>4.374976974839259</v>
       </c>
       <c r="C4" t="n">
-        <v>6.583344524195973</v>
+        <v>6.466952971458562</v>
       </c>
       <c r="D4" t="n">
-        <v>6.027192948259752</v>
+        <v>4.371970914872202</v>
       </c>
       <c r="E4" t="n">
-        <v>4.057322115130065</v>
+        <v>2.976065604110701</v>
       </c>
       <c r="F4" t="n">
-        <v>4.083551077453866</v>
+        <v>4.575735886751183</v>
       </c>
       <c r="G4" t="n">
-        <v>4.009029055229816</v>
+        <v>3.235095665006958</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8112899527527522</v>
+        <v>0.9163331756651127</v>
       </c>
       <c r="I4" t="n">
-        <v>0.802331771348471</v>
+        <v>0.8171894954919763</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8343185476173161</v>
+        <v>0.9164481116233449</v>
       </c>
       <c r="K4" t="n">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.9210526315789473</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.868421052631579</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.868421052631579</v>
-      </c>
       <c r="N4" t="n">
-        <v>3.046994546204955</v>
+        <v>2.828107145766872</v>
       </c>
       <c r="O4" t="n">
-        <v>2.863374008176018</v>
+        <v>3.260711216489097</v>
       </c>
       <c r="P4" t="n">
-        <v>2.858911165334865</v>
+        <v>2.738208893190154</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>raw</t>
@@ -864,32 +864,32 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>-0.1509057681875552</v>
+        <v>-2.091975996619302</v>
       </c>
       <c r="X4" t="n">
-        <v>0.405245807748666</v>
+        <v>0.003006059967057162</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.02622896232380167</v>
+        <v>-1.599670282640481</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04829305990024846</v>
+        <v>-0.259030060896257</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.008958181404281174</v>
+        <v>-0.09914368017313646</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02302859486456388</v>
+        <v>0.0001149359582321985</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1836205380289369</v>
+        <v>-0.432604070722225</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1880833808700899</v>
+        <v>0.08989825257671802</v>
       </c>
     </row>
     <row r="5">
@@ -897,65 +897,65 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8.674899161173299</v>
+        <v>8.70886638360567</v>
       </c>
       <c r="C5" t="n">
-        <v>9.081940871536199</v>
+        <v>9.301305709171794</v>
       </c>
       <c r="D5" t="n">
-        <v>8.732932212263655</v>
+        <v>8.819747079938423</v>
       </c>
       <c r="E5" t="n">
-        <v>4.598109692766424</v>
+        <v>4.575231286547891</v>
       </c>
       <c r="F5" t="n">
-        <v>4.312196512877992</v>
+        <v>4.606729927897392</v>
       </c>
       <c r="G5" t="n">
-        <v>4.284158811659039</v>
+        <v>4.200817963430168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5535801197770819</v>
+        <v>0.5488685354103464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.510703627054825</v>
+        <v>0.4854024655938335</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5475872515059084</v>
+        <v>0.5373078556130113</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="M5" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="N5" t="n">
-        <v>3.58640092600479</v>
+        <v>3.562619423136597</v>
       </c>
       <c r="O5" t="n">
-        <v>3.865735595144014</v>
+        <v>4.215625665586421</v>
       </c>
       <c r="P5" t="n">
-        <v>3.64778039243231</v>
+        <v>3.772374609194014</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>raw</t>
@@ -968,32 +968,32 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>-0.4070417103629005</v>
+        <v>-0.592439325566124</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.05803305109035684</v>
+        <v>-0.1108806963327531</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.285913179888432</v>
+        <v>-0.03149864134950153</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3139508811073846</v>
+        <v>0.3744133231177225</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.04287649272225691</v>
+        <v>-0.06346606981651293</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.005992868271173513</v>
+        <v>-0.0115606797973351</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.279334669139224</v>
+        <v>-0.6530062424498237</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.06137946642751979</v>
+        <v>-0.2097551860574169</v>
       </c>
     </row>
     <row r="6">
@@ -1001,65 +1001,65 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5.08756399556303</v>
+        <v>7.200555316304638</v>
       </c>
       <c r="C6" t="n">
-        <v>3.615246860465641</v>
+        <v>5.963022382229162</v>
       </c>
       <c r="D6" t="n">
-        <v>4.511176073747119</v>
+        <v>6.864462313772571</v>
       </c>
       <c r="E6" t="n">
-        <v>3.61767989150909</v>
+        <v>4.849295187431804</v>
       </c>
       <c r="F6" t="n">
-        <v>2.443816654018256</v>
+        <v>3.513692089861562</v>
       </c>
       <c r="G6" t="n">
-        <v>3.156982989524257</v>
+        <v>4.333580888408722</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8526587550865046</v>
+        <v>0.7220739940459839</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9255987075496919</v>
+        <v>0.8093968459082046</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8841531789080129</v>
+        <v>0.747413430704899</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="L6" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="N6" t="n">
-        <v>3.248142728620511</v>
+        <v>3.609116947517809</v>
       </c>
       <c r="O6" t="n">
-        <v>2.602840858014383</v>
+        <v>2.921716858057386</v>
       </c>
       <c r="P6" t="n">
-        <v>2.912893437997214</v>
+        <v>3.55217636749733</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1072,32 +1072,32 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>1.472317135097389</v>
+        <v>1.237532934075476</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5763879218159103</v>
+        <v>0.336093002532067</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.173863237490834</v>
+        <v>1.335603097570242</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.460696901984833</v>
+        <v>0.5157142990230819</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0729399524631873</v>
+        <v>0.08732285186222066</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03149442382150835</v>
+        <v>0.02533943665891503</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.645301870606128</v>
+        <v>0.6874000894604229</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.3352492906232971</v>
+        <v>0.05694058002047875</v>
       </c>
     </row>
     <row r="7">
@@ -1105,65 +1105,65 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>6.542184398924877</v>
+        <v>6.444313827156663</v>
       </c>
       <c r="C7" t="n">
-        <v>5.345855483652676</v>
+        <v>5.26550166829351</v>
       </c>
       <c r="D7" t="n">
-        <v>5.873572707282979</v>
+        <v>5.555102796303983</v>
       </c>
       <c r="E7" t="n">
-        <v>3.984014124658816</v>
+        <v>3.686905997042022</v>
       </c>
       <c r="F7" t="n">
-        <v>3.184598851807733</v>
+        <v>3.033501454755002</v>
       </c>
       <c r="G7" t="n">
-        <v>3.976357260008071</v>
+        <v>3.727122849744092</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7476631341936628</v>
+        <v>0.7652140719625405</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8315117689294477</v>
+        <v>0.8432533709220184</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7966052022688948</v>
+        <v>0.8255371751108981</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="L7" t="n">
         <v>0.8157894736842105</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="N7" t="n">
-        <v>3.452706254226523</v>
+        <v>3.292905287401746</v>
       </c>
       <c r="O7" t="n">
-        <v>3.23209405291662</v>
+        <v>3.237583107508751</v>
       </c>
       <c r="P7" t="n">
-        <v>3.411724208809004</v>
+        <v>3.367655903118274</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1176,32 +1176,32 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>1.196328915272201</v>
+        <v>1.178812158863153</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6686116916418978</v>
+        <v>0.8892110308526799</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.7994152728510828</v>
+        <v>0.6534045422870203</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007656864650744666</v>
+        <v>-0.04021685270206987</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.08384863473578485</v>
+        <v>0.07803929895947781</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04894206807523194</v>
+        <v>0.06032310314835754</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.220612201309903</v>
+        <v>0.05532217989299504</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.04098204541751915</v>
+        <v>-0.07475061571652786</v>
       </c>
     </row>
     <row r="8">
@@ -1209,65 +1209,65 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4.337924783224582</v>
+        <v>3.964714909845503</v>
       </c>
       <c r="C8" t="n">
-        <v>6.634657759434549</v>
+        <v>2.765361192658774</v>
       </c>
       <c r="D8" t="n">
-        <v>6.469605257333066</v>
+        <v>3.202070770378133</v>
       </c>
       <c r="E8" t="n">
-        <v>3.22766013396801</v>
+        <v>3.033327032997289</v>
       </c>
       <c r="F8" t="n">
-        <v>4.623077429117012</v>
+        <v>2.145310879633259</v>
       </c>
       <c r="G8" t="n">
-        <v>4.567633501467689</v>
+        <v>2.458650158565442</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9067944044139479</v>
+        <v>0.9103927101961745</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7819706290888214</v>
+        <v>0.9564063591418328</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7926836675691558</v>
+        <v>0.9415504372602672</v>
       </c>
       <c r="K8" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="N8" t="n">
-        <v>3.004004496756056</v>
+        <v>3.001668945305479</v>
       </c>
       <c r="O8" t="n">
-        <v>3.179043616403435</v>
+        <v>2.581926594970477</v>
       </c>
       <c r="P8" t="n">
-        <v>3.394142803553662</v>
+        <v>2.713182588515705</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1280,32 +1280,32 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>-2.296732976209967</v>
+        <v>1.199353717186729</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.131680474108483</v>
+        <v>0.76264413946737</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.395417295149001</v>
+        <v>0.8880161533640298</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.339973367499679</v>
+        <v>0.5746768744318467</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1248237753251265</v>
+        <v>0.04601364894565829</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.1141107368447921</v>
+        <v>0.0311577270640927</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1750391196473791</v>
+        <v>0.4197423503350017</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.3901383067976059</v>
+        <v>0.288486356789774</v>
       </c>
     </row>
     <row r="9">
@@ -1313,65 +1313,65 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>5.668227921117629</v>
+        <v>5.032715298310594</v>
       </c>
       <c r="C9" t="n">
-        <v>5.409501545385683</v>
+        <v>5.638108655223808</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1112923439156</v>
+        <v>6.646990718984054</v>
       </c>
       <c r="E9" t="n">
-        <v>3.558824470269362</v>
+        <v>3.533782940508183</v>
       </c>
       <c r="F9" t="n">
-        <v>3.066279434987569</v>
+        <v>3.446347519522941</v>
       </c>
       <c r="G9" t="n">
-        <v>3.764193719686416</v>
+        <v>4.465730512240301</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8621096461921124</v>
+        <v>0.8879738197825944</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8744103719370483</v>
+        <v>0.8594011772320475</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8397103817003244</v>
+        <v>0.8045818278365214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.868421052631579</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="N9" t="n">
-        <v>3.044721597649217</v>
+        <v>2.917957233149727</v>
       </c>
       <c r="O9" t="n">
-        <v>2.722677612142297</v>
+        <v>2.679723246249941</v>
       </c>
       <c r="P9" t="n">
-        <v>3.113520621482067</v>
+        <v>3.283955372875474</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1384,32 +1384,32 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>0.2587263757319462</v>
+        <v>-0.6053933569132148</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4430644227979705</v>
+        <v>-1.614275420673461</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4925450352817933</v>
+        <v>0.08743542098524193</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.2053692494170538</v>
+        <v>-0.9319475717321177</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0123007257449359</v>
+        <v>-0.02857264255054692</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.02239926449178797</v>
+        <v>-0.08339199194607294</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3220439855069199</v>
+        <v>0.238233986899786</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.06879902383285019</v>
+        <v>-0.3659981397257468</v>
       </c>
     </row>
     <row r="10">
@@ -1417,65 +1417,65 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>5.508807864628655</v>
+        <v>4.737629485237294</v>
       </c>
       <c r="C10" t="n">
-        <v>5.852233492437606</v>
+        <v>4.379791298761032</v>
       </c>
       <c r="D10" t="n">
-        <v>6.261354471033019</v>
+        <v>4.869662803380247</v>
       </c>
       <c r="E10" t="n">
-        <v>3.540617490713446</v>
+        <v>3.197030965317254</v>
       </c>
       <c r="F10" t="n">
-        <v>3.780383692376779</v>
+        <v>2.883743210478898</v>
       </c>
       <c r="G10" t="n">
-        <v>4.114904239625824</v>
+        <v>3.241683366424146</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8475873820120631</v>
+        <v>0.8946994840014267</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8279918745924193</v>
+        <v>0.9100056703448622</v>
       </c>
       <c r="J10" t="n">
-        <v>0.80310156955409</v>
+        <v>0.8887484442000932</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="L10" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="M10" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="M10" t="n">
-        <v>0.9210526315789473</v>
-      </c>
       <c r="N10" t="n">
-        <v>2.922154173974625</v>
+        <v>2.93761739002503</v>
       </c>
       <c r="O10" t="n">
-        <v>2.919210325952539</v>
+        <v>2.813886305768737</v>
       </c>
       <c r="P10" t="n">
-        <v>2.903177498008637</v>
+        <v>2.878198536447836</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>-0.3434256278089514</v>
+        <v>0.3578381864762621</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7525466064043638</v>
+        <v>-0.1320333181429527</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2397662016633331</v>
+        <v>0.3132877548383561</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.5742867489123782</v>
+        <v>-0.04465240110689184</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.01959550741964378</v>
+        <v>0.0153061863434355</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.04448581245797312</v>
+        <v>-0.005951039801333491</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002943848022086026</v>
+        <v>0.1237310842562929</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01897667596598795</v>
+        <v>0.05941885357719379</v>
       </c>
     </row>
     <row r="11">
@@ -1521,65 +1521,65 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4.470242050830411</v>
+        <v>6.062534352379727</v>
       </c>
       <c r="C11" t="n">
-        <v>4.0307653234235</v>
+        <v>6.401187446895227</v>
       </c>
       <c r="D11" t="n">
-        <v>3.435699945788328</v>
+        <v>6.122392489030665</v>
       </c>
       <c r="E11" t="n">
-        <v>3.045826774233905</v>
+        <v>3.802048046738026</v>
       </c>
       <c r="F11" t="n">
-        <v>3.014083736623574</v>
+        <v>4.156776015381924</v>
       </c>
       <c r="G11" t="n">
-        <v>2.554919966634869</v>
+        <v>3.615410215749524</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8915126398308841</v>
+        <v>0.8013324897208376</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9117952263502563</v>
+        <v>0.7785174505219896</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9359163088703291</v>
+        <v>0.7973900547035655</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="M11" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N11" t="n">
-        <v>3.021408206926941</v>
+        <v>3.267546283436297</v>
       </c>
       <c r="O11" t="n">
-        <v>2.742519240193805</v>
+        <v>3.057356585354717</v>
       </c>
       <c r="P11" t="n">
-        <v>2.656411192467226</v>
+        <v>3.047571849275269</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1592,32 +1592,32 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>0.4394767274069107</v>
+        <v>-0.3386530945155002</v>
       </c>
       <c r="X11" t="n">
-        <v>1.034542105042083</v>
+        <v>-0.05985813665093875</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03174303761033093</v>
+        <v>-0.354727968643898</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4909068075990359</v>
+        <v>0.1866378309885022</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0202825865193722</v>
+        <v>-0.02281503919884798</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04440366903944493</v>
+        <v>-0.003942435017272095</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.278888966733136</v>
+        <v>0.2101896980815798</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.364997014459715</v>
+        <v>0.2199744341610281</v>
       </c>
     </row>
     <row r="12">
@@ -1625,65 +1625,65 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>6.113735240455723</v>
+        <v>5.225236888662945</v>
       </c>
       <c r="C12" t="n">
-        <v>4.963328745699875</v>
+        <v>4.31461556338385</v>
       </c>
       <c r="D12" t="n">
-        <v>4.445493447341658</v>
+        <v>4.50142908688374</v>
       </c>
       <c r="E12" t="n">
-        <v>4.297190364631804</v>
+        <v>3.677005982861562</v>
       </c>
       <c r="F12" t="n">
-        <v>3.428022104478173</v>
+        <v>3.026977114337348</v>
       </c>
       <c r="G12" t="n">
-        <v>2.895310681256621</v>
+        <v>3.107208429140492</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8157771074705142</v>
+        <v>0.8739339378278662</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8785838590002792</v>
+        <v>0.9140451413731698</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9025974580198853</v>
+        <v>0.9064406825641377</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="N12" t="n">
-        <v>4.339178426569191</v>
+        <v>3.579640953040565</v>
       </c>
       <c r="O12" t="n">
-        <v>2.846026227915389</v>
+        <v>2.679198337969107</v>
       </c>
       <c r="P12" t="n">
-        <v>2.734550542593082</v>
+        <v>2.921086174988108</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>1.150406494755848</v>
+        <v>0.9106213252790951</v>
       </c>
       <c r="X12" t="n">
-        <v>1.668241793114065</v>
+        <v>0.7238078017792047</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8691682601536312</v>
+        <v>0.6500288685242142</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.401879683375183</v>
+        <v>0.5697975537210702</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.062806751529765</v>
+        <v>0.04011120354530362</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.08682035054937109</v>
+        <v>0.03250674473627146</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.493152198653802</v>
+        <v>0.9004426150714582</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.604627883976109</v>
+        <v>0.6585547780524572</v>
       </c>
     </row>
     <row r="13">
@@ -1729,65 +1729,65 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>5.253263398924828</v>
+        <v>5.513619108308549</v>
       </c>
       <c r="C13" t="n">
-        <v>5.67161989924397</v>
+        <v>6.956751646141506</v>
       </c>
       <c r="D13" t="n">
-        <v>5.423082023326805</v>
+        <v>6.426224317335607</v>
       </c>
       <c r="E13" t="n">
-        <v>3.599845403285212</v>
+        <v>3.452746216863343</v>
       </c>
       <c r="F13" t="n">
-        <v>3.422611291572288</v>
+        <v>3.798361997147868</v>
       </c>
       <c r="G13" t="n">
-        <v>3.571793647959566</v>
+        <v>3.416677426357614</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8625566343233695</v>
+        <v>0.8374170162185711</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8397936732617313</v>
+        <v>0.7411700271604744</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8535269334684016</v>
+        <v>0.7791419007326796</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="N13" t="n">
-        <v>2.910072852533138</v>
+        <v>2.978544839999224</v>
       </c>
       <c r="O13" t="n">
-        <v>2.751900168654548</v>
+        <v>3.04092946512249</v>
       </c>
       <c r="P13" t="n">
-        <v>2.737325207851953</v>
+        <v>2.867285899030742</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>-0.4183565003191418</v>
+        <v>-1.443132537832957</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1698186244019775</v>
+        <v>-0.912605209027058</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1772341117129241</v>
+        <v>-0.345615780284525</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02805175532564608</v>
+        <v>0.03606879050572909</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.02276296106163822</v>
+        <v>-0.0962469890580967</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.009029700854967904</v>
+        <v>-0.05827511548589148</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1581726838785897</v>
+        <v>-0.06238462512326626</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1727476446811846</v>
+        <v>0.1112589409684817</v>
       </c>
     </row>
     <row r="14">
@@ -1833,65 +1833,65 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>4.472924127013219</v>
+        <v>4.383599238085628</v>
       </c>
       <c r="C14" t="n">
-        <v>3.417526515611109</v>
+        <v>3.52253253463554</v>
       </c>
       <c r="D14" t="n">
-        <v>3.751667581709983</v>
+        <v>4.311073244524787</v>
       </c>
       <c r="E14" t="n">
-        <v>3.447351679629355</v>
+        <v>3.351192339653753</v>
       </c>
       <c r="F14" t="n">
-        <v>2.490704835160654</v>
+        <v>2.501334311212317</v>
       </c>
       <c r="G14" t="n">
-        <v>2.754345202046309</v>
+        <v>3.051845049457989</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8859154592868815</v>
+        <v>0.8895734447456137</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9334010286826131</v>
+        <v>0.9286946911898196</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9197412416631177</v>
+        <v>0.8931971991269569</v>
       </c>
       <c r="K14" t="n">
         <v>0.9736842105263158</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N14" t="n">
-        <v>2.836818844560698</v>
+        <v>2.860786748614288</v>
       </c>
       <c r="O14" t="n">
-        <v>2.577190104806323</v>
+        <v>2.651187388085126</v>
       </c>
       <c r="P14" t="n">
-        <v>2.694031659801693</v>
+        <v>2.89932505733121</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>raw</t>
@@ -1904,32 +1904,32 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>1.05539761140211</v>
+        <v>0.8610667034500881</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7212565453032362</v>
+        <v>0.07252599356084133</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.9566468444687009</v>
+        <v>0.8498580284414357</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.693006477583046</v>
+        <v>0.2993472901957639</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.04748556939573156</v>
+        <v>0.03912124644420589</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.03382578237623612</v>
+        <v>0.003623754381343214</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2596287397543748</v>
+        <v>0.2095993605291619</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1427871847590048</v>
+        <v>-0.03853830871692221</v>
       </c>
     </row>
     <row r="15">
@@ -1937,65 +1937,65 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>6.072584928528743</v>
+        <v>4.647890976705044</v>
       </c>
       <c r="C15" t="n">
-        <v>5.961401105380534</v>
+        <v>3.833504761677382</v>
       </c>
       <c r="D15" t="n">
-        <v>6.512242099005349</v>
+        <v>4.107066258627672</v>
       </c>
       <c r="E15" t="n">
-        <v>4.035927127647771</v>
+        <v>3.183166672266097</v>
       </c>
       <c r="F15" t="n">
-        <v>3.391577466896543</v>
+        <v>2.451363390966522</v>
       </c>
       <c r="G15" t="n">
-        <v>3.977463275982398</v>
+        <v>2.72082670145035</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8268879397719164</v>
+        <v>0.9027871664497031</v>
       </c>
       <c r="I15" t="n">
-        <v>0.833168975111489</v>
+        <v>0.9338692038481911</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8009137779700037</v>
+        <v>0.9240941661010925</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="L15" t="n">
         <v>0.9210526315789473</v>
       </c>
       <c r="M15" t="n">
-        <v>0.868421052631579</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="N15" t="n">
-        <v>3.003418148722262</v>
+        <v>2.916411026774047</v>
       </c>
       <c r="O15" t="n">
-        <v>2.824775078204969</v>
+        <v>2.70588214262251</v>
       </c>
       <c r="P15" t="n">
-        <v>3.010461229416753</v>
+        <v>2.740234278390495</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2008,32 +2008,32 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>0.1111838231482087</v>
+        <v>0.8143862150276622</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4396571704766066</v>
+        <v>0.5408247180773724</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6443496607512276</v>
+        <v>0.7318032812995749</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0584638516653726</v>
+        <v>0.462339970815747</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.006281035339572583</v>
+        <v>0.03108203739848792</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.0259741618019127</v>
+        <v>0.02130699965138938</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.178643070517293</v>
+        <v>0.2105288841515369</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.007043080694491</v>
+        <v>0.1761767483835519</v>
       </c>
     </row>
     <row r="16">
@@ -2041,65 +2041,65 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>7.546781278822898</v>
+        <v>7.505687363155473</v>
       </c>
       <c r="C16" t="n">
-        <v>6.780404206755098</v>
+        <v>6.813660564300319</v>
       </c>
       <c r="D16" t="n">
-        <v>6.982675116485544</v>
+        <v>6.954094463969433</v>
       </c>
       <c r="E16" t="n">
-        <v>4.330109874618512</v>
+        <v>4.314682604336021</v>
       </c>
       <c r="F16" t="n">
-        <v>3.542645935311109</v>
+        <v>3.728340272849755</v>
       </c>
       <c r="G16" t="n">
-        <v>4.041879918901512</v>
+        <v>4.181731956448925</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6747188355655578</v>
+        <v>0.6675369307837824</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7374291207703707</v>
+        <v>0.7260171003298079</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7215295855243807</v>
+        <v>0.7146067874229716</v>
       </c>
       <c r="K16" t="n">
         <v>0.8421052631578947</v>
       </c>
       <c r="L16" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="N16" t="n">
-        <v>3.584276008587242</v>
+        <v>3.528811251865215</v>
       </c>
       <c r="O16" t="n">
-        <v>3.758177987210609</v>
+        <v>3.986754082665996</v>
       </c>
       <c r="P16" t="n">
-        <v>3.744722198596475</v>
+        <v>3.916363545959896</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2112,32 +2112,32 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>0.7663770720678</v>
+        <v>0.6920267988551538</v>
       </c>
       <c r="X16" t="n">
-        <v>0.564106162337354</v>
+        <v>0.5515928991860397</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.7874639393074032</v>
+        <v>0.5863423314862657</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.2882299557170001</v>
+        <v>0.1329506478870961</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.06271028520481292</v>
+        <v>0.05848016954602553</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.04681074995882295</v>
+        <v>0.04706985663918917</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.1739019786233671</v>
+        <v>-0.4579428308007811</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1604461900092331</v>
+        <v>-0.3875522940946809</v>
       </c>
     </row>
     <row r="17">
@@ -2145,65 +2145,65 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>7.045814908460007</v>
+        <v>7.56815880448688</v>
       </c>
       <c r="C17" t="n">
-        <v>7.941037165537644</v>
+        <v>7.622340747225163</v>
       </c>
       <c r="D17" t="n">
-        <v>7.834425041964809</v>
+        <v>7.321076520218012</v>
       </c>
       <c r="E17" t="n">
-        <v>4.637253551481415</v>
+        <v>4.934636625729475</v>
       </c>
       <c r="F17" t="n">
-        <v>3.924309843701572</v>
+        <v>4.514673118041169</v>
       </c>
       <c r="G17" t="n">
-        <v>4.284745217754694</v>
+        <v>4.453141336109529</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7444632419416413</v>
+        <v>0.6924351839145518</v>
       </c>
       <c r="I17" t="n">
-        <v>0.675402345391353</v>
+        <v>0.6880155854991197</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6840595883705631</v>
+        <v>0.7121898722236659</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="M17" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N17" t="n">
-        <v>3.516679824590609</v>
+        <v>3.463343446331268</v>
       </c>
       <c r="O17" t="n">
-        <v>3.357328649127099</v>
+        <v>4.284151419826864</v>
       </c>
       <c r="P17" t="n">
-        <v>3.358502406448152</v>
+        <v>3.937082943182012</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2216,32 +2216,32 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>-0.8952222570776369</v>
+        <v>-0.05418194273828281</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7886101335048021</v>
+        <v>0.2470822842688678</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.7129437077798424</v>
+        <v>0.4199635076883057</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.3525083337267203</v>
+        <v>0.4814952896199456</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.06906089655028824</v>
+        <v>-0.004419598415432158</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.06040365357107813</v>
+        <v>0.01975468830911409</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.15935117546351</v>
+        <v>-0.8208079734955964</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1581774181424569</v>
+        <v>-0.4737394968507438</v>
       </c>
     </row>
     <row r="18">
@@ -2249,65 +2249,65 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>4.778554674690114</v>
+        <v>5.498646242280503</v>
       </c>
       <c r="C18" t="n">
-        <v>5.099536443306097</v>
+        <v>5.731666045208391</v>
       </c>
       <c r="D18" t="n">
-        <v>4.530019767499992</v>
+        <v>5.59680905656283</v>
       </c>
       <c r="E18" t="n">
-        <v>3.649952801242564</v>
+        <v>4.168289324878258</v>
       </c>
       <c r="F18" t="n">
-        <v>3.69145972927603</v>
+        <v>3.986234517912241</v>
       </c>
       <c r="G18" t="n">
-        <v>3.553763929321206</v>
+        <v>4.100473589531927</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8969726822385731</v>
+        <v>0.8696199418071658</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8826668651427023</v>
+        <v>0.8583353910543213</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9074109839490965</v>
+        <v>0.8649232535003405</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M18" t="n">
         <v>0.8421052631578947</v>
       </c>
       <c r="N18" t="n">
-        <v>2.951032770002687</v>
+        <v>3.010686288615655</v>
       </c>
       <c r="O18" t="n">
-        <v>3.010588503002682</v>
+        <v>3.117350369232956</v>
       </c>
       <c r="P18" t="n">
-        <v>2.886593275250503</v>
+        <v>3.142008983637111</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2320,32 +2320,32 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>-0.320981768615983</v>
+        <v>-0.2330198029278883</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2485349071901224</v>
+        <v>-0.0981628142823272</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.04150692803346567</v>
+        <v>0.1820548069660171</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.09618887192135794</v>
+        <v>0.0678157353463309</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.01430581709587075</v>
+        <v>-0.01128455075284451</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0104383017105234</v>
+        <v>-0.004696688306825347</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.05955573299999495</v>
+        <v>-0.1066640806173007</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.06443949475218425</v>
+        <v>-0.1313226950214559</v>
       </c>
     </row>
     <row r="19">
@@ -2353,65 +2353,65 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>4.932279606666009</v>
+        <v>5.346272450663907</v>
       </c>
       <c r="C19" t="n">
-        <v>4.134691418228194</v>
+        <v>4.024761671533609</v>
       </c>
       <c r="D19" t="n">
-        <v>4.107623284964235</v>
+        <v>4.399779561505094</v>
       </c>
       <c r="E19" t="n">
-        <v>3.292200419055009</v>
+        <v>3.818021073536585</v>
       </c>
       <c r="F19" t="n">
-        <v>3.022643989371495</v>
+        <v>2.81756533796906</v>
       </c>
       <c r="G19" t="n">
-        <v>2.698742066223183</v>
+        <v>3.021933956515006</v>
       </c>
       <c r="H19" t="n">
-        <v>0.873582180518684</v>
+        <v>0.8387085515448409</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9111619282179604</v>
+        <v>0.9085908848393651</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9123212938357756</v>
+        <v>0.8907626882555109</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="N19" t="n">
-        <v>2.948069579768821</v>
+        <v>3.057247339906686</v>
       </c>
       <c r="O19" t="n">
-        <v>2.826558156906775</v>
+        <v>2.839030947026502</v>
       </c>
       <c r="P19" t="n">
-        <v>2.820812751538975</v>
+        <v>3.082135875223788</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W19" t="n">
-        <v>0.7975881884378149</v>
+        <v>1.321510779130298</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8246563217017746</v>
+        <v>0.9464928891588134</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2695564296835142</v>
+        <v>1.000455735567525</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.593458352831826</v>
+        <v>0.7960871170215791</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.03757974769927641</v>
+        <v>0.0698823332945242</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.03873911331709168</v>
+        <v>0.05205413671066994</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1215114228620457</v>
+        <v>0.2182163928801844</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1272568282298456</v>
+        <v>-0.024888535317102</v>
       </c>
     </row>
     <row r="20">
@@ -2457,65 +2457,65 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7.041815440088259</v>
+        <v>4.804239665068394</v>
       </c>
       <c r="C20" t="n">
-        <v>6.314911128608236</v>
+        <v>5.247781695744543</v>
       </c>
       <c r="D20" t="n">
-        <v>6.444711436429952</v>
+        <v>4.973878624972825</v>
       </c>
       <c r="E20" t="n">
-        <v>4.37401241655616</v>
+        <v>3.261805189351025</v>
       </c>
       <c r="F20" t="n">
-        <v>3.864799410788688</v>
+        <v>3.629796296861659</v>
       </c>
       <c r="G20" t="n">
-        <v>4.133205247522888</v>
+        <v>3.266511269320639</v>
       </c>
       <c r="H20" t="n">
-        <v>0.745292194197038</v>
+        <v>0.8811587153769789</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7951634446888853</v>
+        <v>0.8582021880686879</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7866562469377812</v>
+        <v>0.8726179086056995</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N20" t="n">
-        <v>2.999412445357485</v>
+        <v>2.960476130914255</v>
       </c>
       <c r="O20" t="n">
-        <v>2.710886420135257</v>
+        <v>2.794442671725243</v>
       </c>
       <c r="P20" t="n">
-        <v>2.97550977747442</v>
+        <v>3.071242003530152</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2528,32 +2528,32 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W20" t="n">
-        <v>0.7269043114800233</v>
+        <v>-0.4435420306761486</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5971040036583073</v>
+        <v>-0.1696389599044306</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5092130057674717</v>
+        <v>-0.3679911075106341</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.240807169033272</v>
+        <v>-0.004706079969614141</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.04987125049184737</v>
+        <v>-0.02295652730829101</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.04136405274074328</v>
+        <v>-0.00854080677127933</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2885260252222279</v>
+        <v>0.1660334591890118</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.02390266788306494</v>
+        <v>-0.1107658726158971</v>
       </c>
     </row>
     <row r="21">
@@ -2561,65 +2561,65 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>5.416252210034576</v>
+        <v>6.877064861243396</v>
       </c>
       <c r="C21" t="n">
-        <v>4.759701688245647</v>
+        <v>6.450727013496472</v>
       </c>
       <c r="D21" t="n">
-        <v>4.835933321707163</v>
+        <v>6.274119108517319</v>
       </c>
       <c r="E21" t="n">
-        <v>3.695798316331693</v>
+        <v>4.240688080622677</v>
       </c>
       <c r="F21" t="n">
-        <v>3.431646829178284</v>
+        <v>3.507140792024067</v>
       </c>
       <c r="G21" t="n">
-        <v>3.572834045481146</v>
+        <v>3.666968168136867</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8347972576314132</v>
+        <v>0.7448731002385269</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8724210678789541</v>
+        <v>0.77552533206135</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8683017202823321</v>
+        <v>0.7876484041805825</v>
       </c>
       <c r="K21" t="n">
         <v>0.8421052631578947</v>
       </c>
       <c r="L21" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="N21" t="n">
-        <v>3.113578098539247</v>
+        <v>3.280668629679115</v>
       </c>
       <c r="O21" t="n">
-        <v>2.897543080845396</v>
+        <v>2.86965454873965</v>
       </c>
       <c r="P21" t="n">
-        <v>2.972442147679018</v>
+        <v>2.836832169486991</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2632,32 +2632,32 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W21" t="n">
-        <v>0.6565505217889287</v>
+        <v>0.4263378477469244</v>
       </c>
       <c r="X21" t="n">
-        <v>0.5803188883274126</v>
+        <v>0.6029457527260771</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2641514871534092</v>
+        <v>0.7335472885986101</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1229642708505474</v>
+        <v>0.5737199124858101</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.03762381024754091</v>
+        <v>0.03065223182282306</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.03350446265091889</v>
+        <v>0.04277530394205553</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.216035017693851</v>
+        <v>0.4110140809394651</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.141135950860229</v>
+        <v>0.4438364601921241</v>
       </c>
     </row>
     <row r="22">
@@ -2665,65 +2665,65 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>8.235717002096429</v>
+        <v>8.604197756677095</v>
       </c>
       <c r="C22" t="n">
-        <v>7.004616345500769</v>
+        <v>7.324130886417601</v>
       </c>
       <c r="D22" t="n">
-        <v>7.114153023127278</v>
+        <v>7.808950673926466</v>
       </c>
       <c r="E22" t="n">
-        <v>5.156612031787815</v>
+        <v>5.326339580763617</v>
       </c>
       <c r="F22" t="n">
-        <v>3.476380869996458</v>
+        <v>3.917506746819778</v>
       </c>
       <c r="G22" t="n">
-        <v>4.521548951343351</v>
+        <v>4.94171265849552</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6247956497504487</v>
+        <v>0.6355692493256827</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7285850648771777</v>
+        <v>0.7359376754222524</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7200300367142678</v>
+        <v>0.6998214830060777</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="L22" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="N22" t="n">
-        <v>3.84291267904291</v>
+        <v>3.818721606439078</v>
       </c>
       <c r="O22" t="n">
-        <v>3.76711328312511</v>
+        <v>4.018044516672312</v>
       </c>
       <c r="P22" t="n">
-        <v>3.816482570930702</v>
+        <v>4.283741681703817</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2736,32 +2736,32 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>1.23110065659566</v>
+        <v>1.280066870259494</v>
       </c>
       <c r="X22" t="n">
-        <v>1.121563978969151</v>
+        <v>0.7952470827506293</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.680231161791357</v>
+        <v>1.408832833943839</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.6350630804444641</v>
+        <v>0.3846269222680965</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.103789415126729</v>
+        <v>0.1003684260965697</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.09523438696381914</v>
+        <v>0.06425223368039501</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.07579939591779983</v>
+        <v>-0.1993229102332337</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.02643010811220803</v>
+        <v>-0.4650200752647389</v>
       </c>
     </row>
     <row r="23">
@@ -2769,65 +2769,65 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>8.531549276301149</v>
+        <v>3.686459733195118</v>
       </c>
       <c r="C23" t="n">
-        <v>11.85677700111892</v>
+        <v>5.404507934292995</v>
       </c>
       <c r="D23" t="n">
-        <v>11.23933479666314</v>
+        <v>5.265548833674759</v>
       </c>
       <c r="E23" t="n">
-        <v>4.627491895759263</v>
+        <v>2.659176200157099</v>
       </c>
       <c r="F23" t="n">
-        <v>5.718400493704322</v>
+        <v>3.196680797075015</v>
       </c>
       <c r="G23" t="n">
-        <v>5.263448955131425</v>
+        <v>3.168643331796517</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6910357726390952</v>
+        <v>0.935647940954774</v>
       </c>
       <c r="I23" t="n">
-        <v>0.403259250602105</v>
+        <v>0.8616893010920652</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4637916064583878</v>
+        <v>0.868710272152897</v>
       </c>
       <c r="K23" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="M23" t="n">
         <v>0.8157894736842105</v>
       </c>
-      <c r="L23" t="n">
-        <v>0.8157894736842105</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.7894736842105263</v>
-      </c>
       <c r="N23" t="n">
-        <v>3.334824222646459</v>
+        <v>2.83176632883593</v>
       </c>
       <c r="O23" t="n">
-        <v>3.991744671482006</v>
+        <v>3.067071192259444</v>
       </c>
       <c r="P23" t="n">
-        <v>3.739648107667581</v>
+        <v>3.14258761257914</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2840,32 +2840,32 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W23" t="n">
-        <v>-3.32522772481777</v>
+        <v>-1.718048201097877</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.707785520361991</v>
+        <v>-1.579089100479641</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.090908597945059</v>
+        <v>-0.5375045969179162</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.6359570593721617</v>
+        <v>-0.5094671316394179</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.2877765220369902</v>
+        <v>-0.07395863986270879</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.2272441661807074</v>
+        <v>-0.06693766880187701</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.6569204488355473</v>
+        <v>-0.2353048634235138</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.4048238850211221</v>
+        <v>-0.3108212837432101</v>
       </c>
     </row>
     <row r="24">
@@ -2873,65 +2873,65 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>5.340192616797986</v>
+        <v>5.487853894304246</v>
       </c>
       <c r="C24" t="n">
-        <v>4.02445725588523</v>
+        <v>4.003507012836838</v>
       </c>
       <c r="D24" t="n">
-        <v>4.082780294111188</v>
+        <v>3.731568138388827</v>
       </c>
       <c r="E24" t="n">
-        <v>3.231603629302697</v>
+        <v>3.561453188568551</v>
       </c>
       <c r="F24" t="n">
-        <v>2.702790757910856</v>
+        <v>2.69499665639594</v>
       </c>
       <c r="G24" t="n">
-        <v>2.576906162323855</v>
+        <v>2.549106103900518</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8439698455110984</v>
+        <v>0.8289155764153274</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9113845733760013</v>
+        <v>0.9089486106156714</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9087975060402698</v>
+        <v>0.9208978764579936</v>
       </c>
       <c r="K24" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="L24" t="n">
         <v>0.868421052631579</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.8947368421052632</v>
       </c>
       <c r="M24" t="n">
         <v>0.9210526315789473</v>
       </c>
       <c r="N24" t="n">
-        <v>3.174694111963069</v>
+        <v>3.188123978533185</v>
       </c>
       <c r="O24" t="n">
-        <v>2.68318789792124</v>
+        <v>2.731762578456532</v>
       </c>
       <c r="P24" t="n">
-        <v>2.738288221972324</v>
+        <v>2.725129196638743</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>raw</t>
@@ -2944,32 +2944,32 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W24" t="n">
-        <v>1.315735360912756</v>
+        <v>1.484346881467408</v>
       </c>
       <c r="X24" t="n">
-        <v>1.257412322686798</v>
+        <v>1.756285755915419</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.5288128713918407</v>
+        <v>0.8664565321726112</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6546974669788419</v>
+        <v>1.012347084668033</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.06741472786490288</v>
+        <v>0.08003303420034402</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.06482766052917133</v>
+        <v>0.09198230004266617</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4915062140418294</v>
+        <v>0.4563614000766534</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.4364058899907453</v>
+        <v>0.4629947818944422</v>
       </c>
     </row>
     <row r="25">
@@ -2977,65 +2977,65 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>4.870514650847863</v>
+        <v>7.620392157806402</v>
       </c>
       <c r="C25" t="n">
-        <v>5.598818147946197</v>
+        <v>7.503468012040011</v>
       </c>
       <c r="D25" t="n">
-        <v>5.530752375893494</v>
+        <v>7.562022466537921</v>
       </c>
       <c r="E25" t="n">
-        <v>3.373023610478879</v>
+        <v>4.850117239791627</v>
       </c>
       <c r="F25" t="n">
-        <v>3.672206831708625</v>
+        <v>4.747976903359342</v>
       </c>
       <c r="G25" t="n">
-        <v>3.719127084110701</v>
+        <v>4.912495162463125</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8701451264211082</v>
+        <v>0.7068284582300964</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8284063276271628</v>
+        <v>0.715756043915584</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8325531528015699</v>
+        <v>0.7113024523807886</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="N25" t="n">
-        <v>2.976345297156884</v>
+        <v>3.12424670981307</v>
       </c>
       <c r="O25" t="n">
-        <v>2.772519208667387</v>
+        <v>2.893935462156149</v>
       </c>
       <c r="P25" t="n">
-        <v>2.798906086734803</v>
+        <v>3.028424040876993</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T25" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3048,32 +3048,32 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W25" t="n">
-        <v>-0.7283034970983344</v>
+        <v>0.116924145766391</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6602377250456311</v>
+        <v>0.05836969126848057</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.2991832212297463</v>
+        <v>0.1021403364322842</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.346103473631822</v>
+        <v>-0.062377922671498</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.04173879879394538</v>
+        <v>0.008927585685487571</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.03759197361953825</v>
+        <v>0.004473994150692162</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2038260884894969</v>
+        <v>0.2303112476569211</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.1774392104220808</v>
+        <v>0.09582266893607683</v>
       </c>
     </row>
     <row r="26">
@@ -3081,65 +3081,65 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>5.812732100383509</v>
+        <v>5.32114038869814</v>
       </c>
       <c r="C26" t="n">
-        <v>4.881914302740249</v>
+        <v>3.700911052126984</v>
       </c>
       <c r="D26" t="n">
-        <v>5.505331024500489</v>
+        <v>4.0935826133603</v>
       </c>
       <c r="E26" t="n">
-        <v>4.058449455556615</v>
+        <v>3.645745853406134</v>
       </c>
       <c r="F26" t="n">
-        <v>3.05337463490427</v>
+        <v>2.695098663994977</v>
       </c>
       <c r="G26" t="n">
-        <v>3.851190468551333</v>
+        <v>3.054360019776816</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8127101222269729</v>
+        <v>0.8354932324465881</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8678905165877895</v>
+        <v>0.9204222548296993</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8319956348078246</v>
+        <v>0.9026398009030189</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="L26" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="M26" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="N26" t="n">
-        <v>3.091328574457474</v>
+        <v>3.000651671107128</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75918052236599</v>
+        <v>2.797183776362321</v>
       </c>
       <c r="P26" t="n">
-        <v>3.102719874871876</v>
+        <v>2.980119281822857</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3152,32 +3152,32 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>0.9308177976432601</v>
+        <v>1.620229336571156</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3074010758830203</v>
+        <v>1.22755777533784</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.005074820652345</v>
+        <v>0.950647189411157</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.2072589870052819</v>
+        <v>0.5913858336293178</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.05518039436081656</v>
+        <v>0.08492902238311117</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.01928551258085165</v>
+        <v>0.06714656845643074</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.3321480520914837</v>
+        <v>0.203467894744807</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.01139130041440195</v>
+        <v>0.02053238928427126</v>
       </c>
     </row>
     <row r="27">
@@ -3185,65 +3185,65 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>9.954696890948485</v>
+        <v>6.544254006273851</v>
       </c>
       <c r="C27" t="n">
-        <v>10.84130987496052</v>
+        <v>6.671867817184196</v>
       </c>
       <c r="D27" t="n">
-        <v>9.797115128581934</v>
+        <v>6.743204963190506</v>
       </c>
       <c r="E27" t="n">
-        <v>5.251208060125414</v>
+        <v>3.660523016608248</v>
       </c>
       <c r="F27" t="n">
-        <v>5.589888452764375</v>
+        <v>3.804887317355958</v>
       </c>
       <c r="G27" t="n">
-        <v>5.013623546558549</v>
+        <v>4.017825798446564</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6108035257826518</v>
+        <v>0.8203429873632175</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5383888062804014</v>
+        <v>0.8132680012758507</v>
       </c>
       <c r="J27" t="n">
-        <v>0.623027874003115</v>
+        <v>0.8092534903661632</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="M27" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="N27" t="n">
-        <v>3.543170864159883</v>
+        <v>3.091296551262015</v>
       </c>
       <c r="O27" t="n">
-        <v>4.404933209553962</v>
+        <v>4.249473323272803</v>
       </c>
       <c r="P27" t="n">
-        <v>3.815021093804668</v>
+        <v>3.903352485412991</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3256,32 +3256,32 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W27" t="n">
-        <v>-0.8866129840120358</v>
+        <v>-0.1276138109103444</v>
       </c>
       <c r="X27" t="n">
-        <v>0.1575817623665507</v>
+        <v>-0.1989509569166552</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.3386803926389605</v>
+        <v>-0.1443643007477098</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.2375845135668655</v>
+        <v>-0.3573027818383161</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.07241471950225042</v>
+        <v>-0.007074986087366786</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.01222434822046314</v>
+        <v>-0.0110894969970543</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.8617623453940793</v>
+        <v>-1.158176772010788</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.2718502296447847</v>
+        <v>-0.8120559341509761</v>
       </c>
     </row>
     <row r="28">
@@ -3289,65 +3289,65 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>4.970548959219352</v>
+        <v>4.694714885403204</v>
       </c>
       <c r="C28" t="n">
-        <v>3.928754332251961</v>
+        <v>3.623580331478538</v>
       </c>
       <c r="D28" t="n">
-        <v>4.440101855785352</v>
+        <v>4.388664199176995</v>
       </c>
       <c r="E28" t="n">
-        <v>3.670578674845698</v>
+        <v>3.339312425844386</v>
       </c>
       <c r="F28" t="n">
-        <v>2.799859530781669</v>
+        <v>2.519389405345918</v>
       </c>
       <c r="G28" t="n">
-        <v>3.433728319099612</v>
+        <v>3.323885204834498</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8568456694486872</v>
+        <v>0.8712454330113395</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9105654091649225</v>
+        <v>0.923295651520658</v>
       </c>
       <c r="J28" t="n">
-        <v>0.885769613973953</v>
+        <v>0.8874853945006766</v>
       </c>
       <c r="K28" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="L28" t="n">
         <v>0.8157894736842105</v>
       </c>
-      <c r="L28" t="n">
-        <v>0.8421052631578947</v>
-      </c>
       <c r="M28" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N28" t="n">
-        <v>3.22923141094979</v>
+        <v>3.080877974013391</v>
       </c>
       <c r="O28" t="n">
-        <v>2.77008171176228</v>
+        <v>2.683803836278899</v>
       </c>
       <c r="P28" t="n">
-        <v>3.007329318170316</v>
+        <v>3.079111492108765</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3360,32 +3360,32 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W28" t="n">
-        <v>1.041794626967391</v>
+        <v>1.071134553924666</v>
       </c>
       <c r="X28" t="n">
-        <v>0.5304471034339997</v>
+        <v>0.3060506862262091</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.8707191440640289</v>
+        <v>0.819923020498468</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.2368503557460859</v>
+        <v>0.01542722100988803</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.05371973971623523</v>
+        <v>0.05205021850931846</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.02892394452526581</v>
+        <v>0.01623996148933715</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.4591496991875101</v>
+        <v>0.3970741377344917</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.2219020927794744</v>
+        <v>0.001766481904625916</v>
       </c>
     </row>
     <row r="29">
@@ -3393,65 +3393,65 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>4.61067359223495</v>
+        <v>3.829650687019327</v>
       </c>
       <c r="C29" t="n">
-        <v>4.074202546250453</v>
+        <v>4.059261830777651</v>
       </c>
       <c r="D29" t="n">
-        <v>4.836966360020576</v>
+        <v>4.101960044976395</v>
       </c>
       <c r="E29" t="n">
-        <v>3.474824043921486</v>
+        <v>2.960333498338582</v>
       </c>
       <c r="F29" t="n">
-        <v>3.075474059511145</v>
+        <v>3.205167393441803</v>
       </c>
       <c r="G29" t="n">
-        <v>3.543668044478918</v>
+        <v>3.187640688566834</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8645123018697618</v>
+        <v>0.9113797876796534</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8942071443021757</v>
+        <v>0.9004345659735356</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8508864043913977</v>
+        <v>0.8983289490738209</v>
       </c>
       <c r="K29" t="n">
         <v>0.9210526315789473</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="M29" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="N29" t="n">
-        <v>2.93184641319158</v>
+        <v>2.881792080413185</v>
       </c>
       <c r="O29" t="n">
-        <v>2.669560734146152</v>
+        <v>2.726019990712963</v>
       </c>
       <c r="P29" t="n">
-        <v>2.969316247882448</v>
+        <v>2.814618363764942</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T29" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3464,32 +3464,32 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W29" t="n">
-        <v>0.5364710459844968</v>
+        <v>-0.2296111437583241</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.2262927677856261</v>
+        <v>-0.2723093579570679</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.3993499844103408</v>
+        <v>-0.2448338951032212</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.06884400055743223</v>
+        <v>-0.227307190228252</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.02969484243241394</v>
+        <v>-0.01094522170611789</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.01362589747836407</v>
+        <v>-0.01305083860583256</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.2622856790454278</v>
+        <v>0.1557720897002217</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.03746983469086818</v>
+        <v>0.0671737166482429</v>
       </c>
     </row>
     <row r="30">
@@ -3497,65 +3497,65 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>5.193346956391931</v>
+        <v>3.680129656571254</v>
       </c>
       <c r="C30" t="n">
-        <v>4.519057704191289</v>
+        <v>2.615420606841493</v>
       </c>
       <c r="D30" t="n">
-        <v>4.810701174036105</v>
+        <v>3.423758895406687</v>
       </c>
       <c r="E30" t="n">
-        <v>3.669357594092283</v>
+        <v>2.903458957515863</v>
       </c>
       <c r="F30" t="n">
-        <v>3.148867334642262</v>
+        <v>2.09035741471475</v>
       </c>
       <c r="G30" t="n">
-        <v>3.268634000117297</v>
+        <v>2.622783030121734</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8682452060185021</v>
+        <v>0.9314118274882912</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9002374539315718</v>
+        <v>0.9653577513698809</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8869453286177135</v>
+        <v>0.9406351548704109</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="L30" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="M30" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="N30" t="n">
-        <v>2.959770663937167</v>
+        <v>2.837544067895192</v>
       </c>
       <c r="O30" t="n">
-        <v>2.724640678010494</v>
+        <v>2.507938911441812</v>
       </c>
       <c r="P30" t="n">
-        <v>2.865751317772214</v>
+        <v>2.783703362421207</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3568,32 +3568,32 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W30" t="n">
-        <v>0.6742892522006416</v>
+        <v>1.064709049729761</v>
       </c>
       <c r="X30" t="n">
-        <v>0.3826457823558256</v>
+        <v>0.2563707611645669</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5204902594500211</v>
+        <v>0.813101542801113</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.4007235939749862</v>
+        <v>0.2806759273941291</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.03199224791306976</v>
+        <v>0.03394592388158968</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.01870012259921139</v>
+        <v>0.009223327382119728</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.2351299859266729</v>
+        <v>0.32960515645338</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.094019346164953</v>
+        <v>0.05384070547398512</v>
       </c>
     </row>
     <row r="31">
@@ -3601,65 +3601,65 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>5.286848327903298</v>
+        <v>7.255854546209028</v>
       </c>
       <c r="C31" t="n">
-        <v>3.773643215914764</v>
+        <v>6.729308409738088</v>
       </c>
       <c r="D31" t="n">
-        <v>4.005651243294942</v>
+        <v>6.453761077685891</v>
       </c>
       <c r="E31" t="n">
-        <v>4.053821619416714</v>
+        <v>4.563041158604969</v>
       </c>
       <c r="F31" t="n">
-        <v>2.657088905031268</v>
+        <v>4.173694611719833</v>
       </c>
       <c r="G31" t="n">
-        <v>3.102456811176633</v>
+        <v>3.805860301232553</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8628861406985966</v>
+        <v>0.7674263845589591</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9301430973094853</v>
+        <v>0.7999566247261866</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9212892735164003</v>
+        <v>0.8160037062742561</v>
       </c>
       <c r="K31" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="L31" t="n">
-        <v>0.868421052631579</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="N31" t="n">
-        <v>3.084303993746538</v>
+        <v>2.99508354189955</v>
       </c>
       <c r="O31" t="n">
-        <v>2.791550414303669</v>
+        <v>3.156279599206589</v>
       </c>
       <c r="P31" t="n">
-        <v>2.777769801530548</v>
+        <v>2.955552824383202</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T31" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3672,32 +3672,32 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W31" t="n">
-        <v>1.513205111988534</v>
+        <v>0.5265461364709392</v>
       </c>
       <c r="X31" t="n">
-        <v>1.281197084608356</v>
+        <v>0.8020934685231369</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.396732714385446</v>
+        <v>0.389346546885136</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.9513648082400805</v>
+        <v>0.7571808573724161</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.06725695661088871</v>
+        <v>0.0325302401672275</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.05840313281780374</v>
+        <v>0.04857732171529705</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.2927535794428691</v>
+        <v>-0.161196057307039</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.3065341922159903</v>
+        <v>0.03953071751634774</v>
       </c>
     </row>
     <row r="32">
@@ -3705,65 +3705,65 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>4.676125311359915</v>
+        <v>4.553767931023974</v>
       </c>
       <c r="C32" t="n">
-        <v>2.735522102865541</v>
+        <v>2.843386010889343</v>
       </c>
       <c r="D32" t="n">
-        <v>3.489274337405615</v>
+        <v>3.589520386324124</v>
       </c>
       <c r="E32" t="n">
-        <v>3.401808122940323</v>
+        <v>3.559146117915172</v>
       </c>
       <c r="F32" t="n">
-        <v>2.143996383180779</v>
+        <v>2.222227172683024</v>
       </c>
       <c r="G32" t="n">
-        <v>2.82457450699174</v>
+        <v>2.868265734545809</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8661680031612849</v>
+        <v>0.8875780394875283</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9541997200645178</v>
+        <v>0.9561690371786987</v>
       </c>
       <c r="J32" t="n">
-        <v>0.925482563056465</v>
+        <v>0.9301474581223179</v>
       </c>
       <c r="K32" t="n">
         <v>0.9210526315789473</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94749996388601</v>
+        <v>2.967787146570698</v>
       </c>
       <c r="O32" t="n">
-        <v>2.594069320683494</v>
+        <v>2.689461744002168</v>
       </c>
       <c r="P32" t="n">
-        <v>2.787387796275429</v>
+        <v>2.893769567987529</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3776,32 +3776,32 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W32" t="n">
-        <v>1.940603208494374</v>
+        <v>1.710381920134631</v>
       </c>
       <c r="X32" t="n">
-        <v>1.1868509739543</v>
+        <v>0.96424754469985</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.257811739759544</v>
+        <v>1.336918945232148</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.5772336159485834</v>
+        <v>0.6908803833693629</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.08803171690323286</v>
+        <v>0.06859099769117039</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.05931455989518009</v>
+        <v>0.04256941863478958</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.353430643202516</v>
+        <v>0.2783254025685302</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.1601121676105812</v>
+        <v>0.07401757858316937</v>
       </c>
     </row>
     <row r="33">
@@ -3809,65 +3809,65 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3.372797517564932</v>
+        <v>4.954716079367497</v>
       </c>
       <c r="C33" t="n">
-        <v>3.883180014492434</v>
+        <v>5.026689215416541</v>
       </c>
       <c r="D33" t="n">
-        <v>3.053303949646089</v>
+        <v>5.224245591689992</v>
       </c>
       <c r="E33" t="n">
-        <v>2.657866146862497</v>
+        <v>3.358568174088477</v>
       </c>
       <c r="F33" t="n">
-        <v>2.882013593133276</v>
+        <v>3.406681909336769</v>
       </c>
       <c r="G33" t="n">
-        <v>2.358719663183115</v>
+        <v>3.396968448796584</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9417382308663675</v>
+        <v>0.8685742064317508</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9227713974265908</v>
+        <v>0.8647282427510289</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9522533168150162</v>
+        <v>0.8538865377834979</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="N33" t="n">
-        <v>2.799733276012869</v>
+        <v>2.943456852039624</v>
       </c>
       <c r="O33" t="n">
-        <v>2.878724931419587</v>
+        <v>3.184400825782061</v>
       </c>
       <c r="P33" t="n">
-        <v>2.587756742279073</v>
+        <v>3.163474640799208</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T33" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3880,32 +3880,32 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>-0.5103824969275021</v>
+        <v>-0.07197313604904387</v>
       </c>
       <c r="X33" t="n">
-        <v>0.3194935679188431</v>
+        <v>-0.269529512322495</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.2241474462707789</v>
+        <v>-0.04811373524829188</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2991464836793822</v>
+        <v>-0.03840027470810714</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.01896683343977679</v>
+        <v>-0.003845963680721876</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.01051508594864869</v>
+        <v>-0.01468766864825288</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.07899165540671804</v>
+        <v>-0.240943973742437</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.2119765337337958</v>
+        <v>-0.2200177887595838</v>
       </c>
     </row>
     <row r="34">
@@ -3913,65 +3913,65 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7.526441552259505</v>
+        <v>6.926659470325902</v>
       </c>
       <c r="C34" t="n">
-        <v>9.857038223070738</v>
+        <v>6.006510234445626</v>
       </c>
       <c r="D34" t="n">
-        <v>9.268802053871807</v>
+        <v>6.27399067565282</v>
       </c>
       <c r="E34" t="n">
-        <v>4.280419968155865</v>
+        <v>4.19773333228787</v>
       </c>
       <c r="F34" t="n">
-        <v>5.204252385712925</v>
+        <v>3.847291152757895</v>
       </c>
       <c r="G34" t="n">
-        <v>4.933624870971811</v>
+        <v>4.393215793490469</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7202726164420968</v>
+        <v>0.7449817664068994</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5202129986576629</v>
+        <v>0.8082355931570901</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5757685990815465</v>
+        <v>0.7907760984308658</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="L34" t="n">
         <v>0.7631578947368421</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="N34" t="n">
-        <v>3.565454088943273</v>
+        <v>3.505084632890161</v>
       </c>
       <c r="O34" t="n">
-        <v>4.005011199367868</v>
+        <v>3.472065669095281</v>
       </c>
       <c r="P34" t="n">
-        <v>3.816891177573138</v>
+        <v>3.749000799889642</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
           <t>raw</t>
@@ -3984,32 +3984,32 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>-2.330596670811233</v>
+        <v>0.9201492358802756</v>
       </c>
       <c r="X34" t="n">
-        <v>-1.742360501612302</v>
+        <v>0.6526687946730814</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.92383241755706</v>
+        <v>0.3504421795299746</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.6532049028159461</v>
+        <v>-0.1954824612025998</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.2000596177844339</v>
+        <v>0.06325382675019076</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.1445040173605503</v>
+        <v>0.04579433202396643</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.4395571104245946</v>
+        <v>0.03301896379487967</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.2514370886298649</v>
+        <v>-0.2439161669994814</v>
       </c>
     </row>
     <row r="35">
@@ -4017,65 +4017,65 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>4.917355218319303</v>
+        <v>5.0844588037344</v>
       </c>
       <c r="C35" t="n">
-        <v>5.282401809594663</v>
+        <v>4.20748849068021</v>
       </c>
       <c r="D35" t="n">
-        <v>5.056403901374706</v>
+        <v>4.327154190512665</v>
       </c>
       <c r="E35" t="n">
-        <v>3.818213995042788</v>
+        <v>3.96930551259979</v>
       </c>
       <c r="F35" t="n">
-        <v>3.266081773570968</v>
+        <v>2.936144433931672</v>
       </c>
       <c r="G35" t="n">
-        <v>3.72790955600955</v>
+        <v>3.346644687527275</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8576347988335158</v>
+        <v>0.85844697435747</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8357128678426734</v>
+        <v>0.9030661272377362</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8494696061529554</v>
+        <v>0.8974739011745937</v>
       </c>
       <c r="K35" t="n">
         <v>0.8157894736842105</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="N35" t="n">
-        <v>3.092111417971844</v>
+        <v>3.03698292555982</v>
       </c>
       <c r="O35" t="n">
-        <v>2.870607506966063</v>
+        <v>2.618123999561387</v>
       </c>
       <c r="P35" t="n">
-        <v>3.072516109022472</v>
+        <v>2.813426575343128</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4088,32 +4088,32 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W35" t="n">
-        <v>-0.3650465912753607</v>
+        <v>0.8769703130541897</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.1390486830554032</v>
+        <v>0.7573046132217343</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5521322214718198</v>
+        <v>1.033161078668118</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.09030443903323793</v>
+        <v>0.622660825072515</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.02192193099084239</v>
+        <v>0.04461915288026619</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.008165192680560374</v>
+        <v>0.03902692681712372</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.2215039110057808</v>
+        <v>0.4188589259984328</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.01959530894937167</v>
+        <v>0.223556350216692</v>
       </c>
     </row>
     <row r="36">
@@ -4121,31 +4121,31 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>6.114325319622934</v>
+        <v>6.224663526087577</v>
       </c>
       <c r="C36" t="n">
-        <v>6.316587970169463</v>
+        <v>6.636490986585676</v>
       </c>
       <c r="D36" t="n">
-        <v>5.841710426394133</v>
+        <v>6.657908851010693</v>
       </c>
       <c r="E36" t="n">
-        <v>4.297094881659405</v>
+        <v>3.888147349299217</v>
       </c>
       <c r="F36" t="n">
-        <v>3.682881396984408</v>
+        <v>3.535508781188763</v>
       </c>
       <c r="G36" t="n">
-        <v>3.423636231924905</v>
+        <v>3.605583779191219</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8561621929552456</v>
+        <v>0.8474596533811143</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8464884465085087</v>
+        <v>0.8266076289395466</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8687026322964602</v>
+        <v>0.8254866489268203</v>
       </c>
       <c r="K36" t="n">
         <v>0.8947368421052632</v>
@@ -4154,32 +4154,32 @@
         <v>0.8421052631578947</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="N36" t="n">
-        <v>3.073453957536572</v>
+        <v>2.967986234419615</v>
       </c>
       <c r="O36" t="n">
-        <v>2.926655154618349</v>
+        <v>2.677549541484666</v>
       </c>
       <c r="P36" t="n">
-        <v>2.803303333494314</v>
+        <v>2.712817041151506</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4192,32 +4192,32 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W36" t="n">
-        <v>-0.2022626505465288</v>
+        <v>-0.4118274604980989</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2726148932288011</v>
+        <v>-0.4332453249231163</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.6142134846749965</v>
+        <v>0.352638568110454</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.8734586497344994</v>
+        <v>0.2825635701079983</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.009673746446736908</v>
+        <v>-0.02085202444156764</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.01254043934121452</v>
+        <v>-0.02197300445429395</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.146798802918223</v>
+        <v>0.2904366929349491</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.270150624042258</v>
+        <v>0.2551691932681091</v>
       </c>
     </row>
     <row r="37">
@@ -4225,65 +4225,65 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>4.47092669049912</v>
+        <v>4.482086267461924</v>
       </c>
       <c r="C37" t="n">
-        <v>3.898530421086048</v>
+        <v>5.121433296326752</v>
       </c>
       <c r="D37" t="n">
-        <v>4.473759913413768</v>
+        <v>4.422279072915088</v>
       </c>
       <c r="E37" t="n">
-        <v>3.227970678208264</v>
+        <v>3.222014878850345</v>
       </c>
       <c r="F37" t="n">
-        <v>2.737825222588658</v>
+        <v>3.015369904882656</v>
       </c>
       <c r="G37" t="n">
-        <v>3.309276831186263</v>
+        <v>2.751696360406907</v>
       </c>
       <c r="H37" t="n">
-        <v>0.913673696188648</v>
+        <v>0.9091851279048854</v>
       </c>
       <c r="I37" t="n">
-        <v>0.934362821567047</v>
+        <v>0.881428696435938</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9135642516932938</v>
+        <v>0.9115925539492921</v>
       </c>
       <c r="K37" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="L37" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="L37" t="n">
-        <v>0.9473684210526315</v>
-      </c>
       <c r="M37" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="N37" t="n">
-        <v>2.967330699286066</v>
+        <v>2.914702002564182</v>
       </c>
       <c r="O37" t="n">
-        <v>2.633132502032303</v>
+        <v>2.680605000004686</v>
       </c>
       <c r="P37" t="n">
-        <v>2.943484460635739</v>
+        <v>2.673370538486374</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T37" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4296,32 +4296,32 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>0.5723962694130718</v>
+        <v>-0.6393470288648277</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.002833222914648381</v>
+        <v>0.05980719454683658</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4901454556196061</v>
+        <v>0.206644973967689</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.08130615297799881</v>
+        <v>0.4703185184434382</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.02068912537839895</v>
+        <v>-0.02775643146894735</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.0001094444953542162</v>
+        <v>0.002407426044406691</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.3341981972537629</v>
+        <v>0.2340970025594959</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.02384623865032687</v>
+        <v>0.2413314640778079</v>
       </c>
     </row>
     <row r="38">
@@ -4329,65 +4329,65 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>5.713459292600396</v>
+        <v>6.196689669036932</v>
       </c>
       <c r="C38" t="n">
-        <v>5.141182004160425</v>
+        <v>6.325311967057984</v>
       </c>
       <c r="D38" t="n">
-        <v>6.536621907776572</v>
+        <v>7.634986518532897</v>
       </c>
       <c r="E38" t="n">
-        <v>4.088660206392942</v>
+        <v>4.291465804855375</v>
       </c>
       <c r="F38" t="n">
-        <v>3.47110841776335</v>
+        <v>4.121214443422581</v>
       </c>
       <c r="G38" t="n">
-        <v>4.200630309609751</v>
+        <v>4.926369282277081</v>
       </c>
       <c r="H38" t="n">
-        <v>0.831538856793458</v>
+        <v>0.8157649163007168</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8635958994921172</v>
+        <v>0.8080373478194809</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7795002004549266</v>
+        <v>0.7203148610877134</v>
       </c>
       <c r="K38" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="N38" t="n">
-        <v>3.182125461519232</v>
+        <v>3.147350046676796</v>
       </c>
       <c r="O38" t="n">
-        <v>3.03676897699479</v>
+        <v>3.135407385738743</v>
       </c>
       <c r="P38" t="n">
-        <v>3.684320587574697</v>
+        <v>4.028632678496003</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T38" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4400,32 +4400,32 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>0.5722772884399712</v>
+        <v>-0.1286222980210523</v>
       </c>
       <c r="X38" t="n">
-        <v>-0.8231626151761766</v>
+        <v>-1.438296849495965</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.6175517886295916</v>
+        <v>0.1702513614327943</v>
       </c>
       <c r="Z38" t="n">
-        <v>-0.1119701032168088</v>
+        <v>-0.6349034774217062</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.03205704269865928</v>
+        <v>-0.007727568481235902</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.05203865633853133</v>
+        <v>-0.09545005521300343</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.1453564845244419</v>
+        <v>0.01194266093805307</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.5021951260554651</v>
+        <v>-0.8812826318192073</v>
       </c>
     </row>
     <row r="39">
@@ -4433,65 +4433,65 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>5.980780953374342</v>
+        <v>4.875633813813501</v>
       </c>
       <c r="C39" t="n">
-        <v>4.365784450498774</v>
+        <v>4.648902889237574</v>
       </c>
       <c r="D39" t="n">
-        <v>4.476757490913983</v>
+        <v>4.479645181379914</v>
       </c>
       <c r="E39" t="n">
-        <v>3.808120442123192</v>
+        <v>3.410275202520106</v>
       </c>
       <c r="F39" t="n">
-        <v>2.967006924458927</v>
+        <v>3.29110961999983</v>
       </c>
       <c r="G39" t="n">
-        <v>3.134435618043403</v>
+        <v>3.164581065220867</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8340879162098973</v>
+        <v>0.8929274409429498</v>
       </c>
       <c r="I39" t="n">
-        <v>0.911592969340539</v>
+        <v>0.9026542556011563</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9070414453312199</v>
+        <v>0.9096135656260117</v>
       </c>
       <c r="K39" t="n">
-        <v>0.868421052631579</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="N39" t="n">
-        <v>3.150914485084818</v>
+        <v>2.978787806720332</v>
       </c>
       <c r="O39" t="n">
-        <v>2.690610496329938</v>
+        <v>2.854800294501587</v>
       </c>
       <c r="P39" t="n">
-        <v>2.800007163302804</v>
+        <v>2.80181596620708</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>1.614996502875568</v>
+        <v>0.2267309245759268</v>
       </c>
       <c r="X39" t="n">
-        <v>1.504023462460359</v>
+        <v>0.3959886324335864</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.8411135176642648</v>
+        <v>0.1191655825202758</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.673684824079789</v>
+        <v>0.2456941372992389</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.07750505313064171</v>
+        <v>0.009726814658206462</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.07295352912132258</v>
+        <v>0.01668612468306185</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.4603039887548799</v>
+        <v>0.1239875122187448</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.3509073217820138</v>
+        <v>0.1769718405132519</v>
       </c>
     </row>
     <row r="40">
@@ -4537,65 +4537,65 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>6.926224584052852</v>
+        <v>6.305307003504442</v>
       </c>
       <c r="C40" t="n">
-        <v>5.893383271459107</v>
+        <v>4.878002787796</v>
       </c>
       <c r="D40" t="n">
-        <v>5.501769920560968</v>
+        <v>4.636918596181915</v>
       </c>
       <c r="E40" t="n">
-        <v>5.291538087104779</v>
+        <v>4.762303134151348</v>
       </c>
       <c r="F40" t="n">
-        <v>4.159016325839097</v>
+        <v>3.396594792227011</v>
       </c>
       <c r="G40" t="n">
-        <v>3.860036118645147</v>
+        <v>3.597476588527453</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7560281241231035</v>
+        <v>0.7970332757350356</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8233653108250416</v>
+        <v>0.8785223290478832</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8460600023402074</v>
+        <v>0.8902331221017392</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="N40" t="n">
-        <v>4.920032926666932</v>
+        <v>3.839293824509659</v>
       </c>
       <c r="O40" t="n">
-        <v>3.194220111181236</v>
+        <v>3.038048559774298</v>
       </c>
       <c r="P40" t="n">
-        <v>3.268574853727669</v>
+        <v>3.670705581526501</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T40" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4608,32 +4608,32 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>1.032841312593745</v>
+        <v>1.427304215708442</v>
       </c>
       <c r="X40" t="n">
-        <v>1.424454663491884</v>
+        <v>1.668388407322527</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.132521761265681</v>
+        <v>1.365708341924337</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.431501968459632</v>
+        <v>1.164826545623895</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.06733718670193811</v>
+        <v>0.08148905331284761</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.0900318782171039</v>
+        <v>0.09319984636670364</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.725812815485696</v>
+        <v>0.801245264735361</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.651458072939263</v>
+        <v>0.1685882429831578</v>
       </c>
     </row>
     <row r="41">
@@ -4641,34 +4641,34 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>9.216285614737711</v>
+        <v>8.10380164800733</v>
       </c>
       <c r="C41" t="n">
-        <v>8.199781053043736</v>
+        <v>6.632496985191713</v>
       </c>
       <c r="D41" t="n">
-        <v>8.340374097419447</v>
+        <v>6.706652167794902</v>
       </c>
       <c r="E41" t="n">
-        <v>5.513179001475764</v>
+        <v>4.812446588130771</v>
       </c>
       <c r="F41" t="n">
-        <v>4.265837579640326</v>
+        <v>3.561327052042181</v>
       </c>
       <c r="G41" t="n">
-        <v>4.670501663879577</v>
+        <v>3.778742063173782</v>
       </c>
       <c r="H41" t="n">
-        <v>0.374988186991622</v>
+        <v>0.5175324108973465</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5052555991986625</v>
+        <v>0.6768198625109563</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4881444259054787</v>
+        <v>0.6695527785776596</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="L41" t="n">
         <v>0.7894736842105263</v>
@@ -4677,29 +4677,29 @@
         <v>0.7894736842105263</v>
       </c>
       <c r="N41" t="n">
-        <v>4.078920551891858</v>
+        <v>3.715894643102795</v>
       </c>
       <c r="O41" t="n">
-        <v>3.628756799724829</v>
+        <v>3.735115251393067</v>
       </c>
       <c r="P41" t="n">
-        <v>3.610503061464019</v>
+        <v>3.644917588555397</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T41" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4712,32 +4712,32 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>1.016504561693974</v>
+        <v>1.471304662815617</v>
       </c>
       <c r="X41" t="n">
-        <v>0.8759115173182632</v>
+        <v>1.397149480212429</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.247341421835437</v>
+        <v>1.25111953608859</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.8426773375961867</v>
+        <v>1.033704524956989</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.1302674122070405</v>
+        <v>0.1592874516136098</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.1131562389138567</v>
+        <v>0.1520203676803131</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.4501637521670285</v>
+        <v>-0.01922060829027217</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.4684174904278389</v>
+        <v>0.07097705454739822</v>
       </c>
     </row>
     <row r="42">
@@ -4745,65 +4745,65 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>7.928041960508544</v>
+        <v>9.88497267444936</v>
       </c>
       <c r="C42" t="n">
-        <v>7.472068326208965</v>
+        <v>9.665829336978874</v>
       </c>
       <c r="D42" t="n">
-        <v>7.426873703722389</v>
+        <v>9.232591575943475</v>
       </c>
       <c r="E42" t="n">
-        <v>4.993182205971865</v>
+        <v>4.947773272054921</v>
       </c>
       <c r="F42" t="n">
-        <v>4.49399526916269</v>
+        <v>5.004537586754605</v>
       </c>
       <c r="G42" t="n">
-        <v>4.605515990375252</v>
+        <v>5.063010404025662</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7023711228461887</v>
+        <v>0.5437921980448291</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7356222788153268</v>
+        <v>0.5637956345116144</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7388107711644426</v>
+        <v>0.602022050560157</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="N42" t="n">
-        <v>3.370296459227086</v>
+        <v>3.616452874122951</v>
       </c>
       <c r="O42" t="n">
-        <v>3.803638293618212</v>
+        <v>4.350726158909681</v>
       </c>
       <c r="P42" t="n">
-        <v>3.636939507764014</v>
+        <v>4.142107008207121</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T42" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4816,32 +4816,32 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>0.4559736342995793</v>
+        <v>0.2191433374704861</v>
       </c>
       <c r="X42" t="n">
-        <v>0.5011682567861548</v>
+        <v>0.6523810985058844</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.499186936809175</v>
+        <v>-0.05676431469968435</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.3876662155966137</v>
+        <v>-0.1152371319707415</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.03325115596913808</v>
+        <v>0.02000343646678526</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.03643964831825386</v>
+        <v>0.05822985251532786</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.4333418343911259</v>
+        <v>-0.7342732847867297</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.266643048536928</v>
+        <v>-0.5256541340841703</v>
       </c>
     </row>
     <row r="43">
@@ -4849,65 +4849,65 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>6.83822766559511</v>
+        <v>5.517114802452486</v>
       </c>
       <c r="C43" t="n">
-        <v>6.338908052487246</v>
+        <v>5.501234437988513</v>
       </c>
       <c r="D43" t="n">
-        <v>6.633442185738816</v>
+        <v>4.636779875207861</v>
       </c>
       <c r="E43" t="n">
-        <v>4.295030004411839</v>
+        <v>3.778836076971393</v>
       </c>
       <c r="F43" t="n">
-        <v>3.98775201896218</v>
+        <v>4.263574619329444</v>
       </c>
       <c r="G43" t="n">
-        <v>4.360657318758679</v>
+        <v>3.623545914758193</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7847677153727137</v>
+        <v>0.8596476550640877</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8150521833460445</v>
+        <v>0.8604544675865293</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7974658783088027</v>
+        <v>0.900864639862023</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="L43" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.868421052631579</v>
       </c>
-      <c r="M43" t="n">
-        <v>0.8157894736842105</v>
-      </c>
       <c r="N43" t="n">
-        <v>3.584623294557471</v>
+        <v>3.295138310758746</v>
       </c>
       <c r="O43" t="n">
-        <v>2.856663409768839</v>
+        <v>3.243698650103342</v>
       </c>
       <c r="P43" t="n">
-        <v>3.147442653532453</v>
+        <v>3.054678906024832</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T43" t="inlineStr">
         <is>
           <t>raw</t>
@@ -4920,32 +4920,32 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>0.4993196131078648</v>
+        <v>0.0158803644639729</v>
       </c>
       <c r="X43" t="n">
-        <v>0.2047854798562945</v>
+        <v>0.8803349272446255</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.3072779854496588</v>
+        <v>-0.484738542358051</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.06562731434684022</v>
+        <v>0.1552901622131997</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03028446797333073</v>
+        <v>0.0008068125224416356</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.01269816293608894</v>
+        <v>0.04121698479793534</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.7279598847886319</v>
+        <v>0.05143966065540395</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.4371806410250181</v>
+        <v>0.2404594047339139</v>
       </c>
     </row>
     <row r="44">
@@ -4953,65 +4953,65 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3.978013666372957</v>
+        <v>3.974162060694979</v>
       </c>
       <c r="C44" t="n">
-        <v>3.668094922790568</v>
+        <v>4.082932536834548</v>
       </c>
       <c r="D44" t="n">
-        <v>3.128959429811382</v>
+        <v>3.294438488930388</v>
       </c>
       <c r="E44" t="n">
-        <v>2.809579587425264</v>
+        <v>2.966134991292257</v>
       </c>
       <c r="F44" t="n">
-        <v>2.518160705370333</v>
+        <v>2.925693586111799</v>
       </c>
       <c r="G44" t="n">
-        <v>2.323291065984555</v>
+        <v>2.446809879693505</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9012992414471237</v>
+        <v>0.8803019268941471</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9160793033521603</v>
+        <v>0.8736601313047705</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9389356395380298</v>
+        <v>0.9177456604800598</v>
       </c>
       <c r="K44" t="n">
         <v>0.9736842105263158</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="N44" t="n">
-        <v>2.833850404613066</v>
+        <v>2.885626118731327</v>
       </c>
       <c r="O44" t="n">
-        <v>2.565030188941534</v>
+        <v>2.652374060464437</v>
       </c>
       <c r="P44" t="n">
-        <v>2.578395889240152</v>
+        <v>2.605994699567425</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T44" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5024,32 +5024,32 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>0.3099187435823891</v>
+        <v>-0.1087704761395689</v>
       </c>
       <c r="X44" t="n">
-        <v>0.849054236561575</v>
+        <v>0.6797235717645909</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.2914188820549306</v>
+        <v>0.04044140518045802</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.4862885214407089</v>
+        <v>0.5193251115987518</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01478006190503656</v>
+        <v>-0.006641795589376609</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.03763639809090613</v>
+        <v>0.03744373358591269</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.268820215671532</v>
+        <v>0.2332520582668898</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.255454515372914</v>
+        <v>0.279631419163902</v>
       </c>
     </row>
     <row r="45">
@@ -5057,65 +5057,65 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>4.394892913280008</v>
+        <v>4.681993230649275</v>
       </c>
       <c r="C45" t="n">
-        <v>3.532197216313349</v>
+        <v>3.441282921853241</v>
       </c>
       <c r="D45" t="n">
-        <v>4.471002422748362</v>
+        <v>4.489725470214556</v>
       </c>
       <c r="E45" t="n">
-        <v>2.963037853615177</v>
+        <v>3.345638334706106</v>
       </c>
       <c r="F45" t="n">
-        <v>2.761175743825</v>
+        <v>2.596408373230187</v>
       </c>
       <c r="G45" t="n">
-        <v>3.190814582945696</v>
+        <v>3.279684876879139</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9021781028155276</v>
+        <v>0.8930274692813827</v>
       </c>
       <c r="I45" t="n">
-        <v>0.936812761680984</v>
+        <v>0.9422101634906326</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8987606619417577</v>
+        <v>0.9016328066504642</v>
       </c>
       <c r="K45" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="M45" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="N45" t="n">
-        <v>2.941228769511402</v>
+        <v>2.9694348857677</v>
       </c>
       <c r="O45" t="n">
-        <v>2.752609227801874</v>
+        <v>2.790873973231369</v>
       </c>
       <c r="P45" t="n">
-        <v>2.973508761243412</v>
+        <v>3.107284510108035</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T45" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5128,32 +5128,32 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W45" t="n">
-        <v>0.8626956969666586</v>
+        <v>1.240710308796034</v>
       </c>
       <c r="X45" t="n">
-        <v>-0.07610950946835437</v>
+        <v>0.1922677604347189</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.2018621097901772</v>
+        <v>0.749229961475919</v>
       </c>
       <c r="Z45" t="n">
-        <v>-0.2277767293305191</v>
+        <v>0.06595345782696693</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.03463465886545647</v>
+        <v>0.04918269420924992</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.003417440873769828</v>
+        <v>0.008605337369081534</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.188619541709528</v>
+        <v>0.178560912536331</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.03227999173201024</v>
+        <v>-0.1378496243403347</v>
       </c>
     </row>
     <row r="46">
@@ -5161,65 +5161,65 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>4.618536507646573</v>
+        <v>4.716276849078954</v>
       </c>
       <c r="C46" t="n">
-        <v>4.566912390974528</v>
+        <v>5.750286837506653</v>
       </c>
       <c r="D46" t="n">
-        <v>5.074392623563073</v>
+        <v>5.960533490396607</v>
       </c>
       <c r="E46" t="n">
-        <v>3.588924878930724</v>
+        <v>3.734813405978221</v>
       </c>
       <c r="F46" t="n">
-        <v>3.292022580315228</v>
+        <v>4.225898886126134</v>
       </c>
       <c r="G46" t="n">
-        <v>3.835278432134094</v>
+        <v>4.432011485665407</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8706304866019253</v>
+        <v>0.8729875987872224</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8735064026342072</v>
+        <v>0.8111893170751332</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8438322630251305</v>
+        <v>0.7971300087936252</v>
       </c>
       <c r="K46" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="L46" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="N46" t="n">
-        <v>3.030252437555037</v>
+        <v>3.065976264700214</v>
       </c>
       <c r="O46" t="n">
-        <v>2.869597335993992</v>
+        <v>3.175414274513324</v>
       </c>
       <c r="P46" t="n">
-        <v>3.152347330234791</v>
+        <v>3.386360003891206</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5232,32 +5232,32 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W46" t="n">
-        <v>0.05162411667204569</v>
+        <v>-1.034009988427699</v>
       </c>
       <c r="X46" t="n">
-        <v>-0.4558561159164993</v>
+        <v>-1.244256641317652</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.2969022986154961</v>
+        <v>-0.491085480147913</v>
       </c>
       <c r="Z46" t="n">
-        <v>-0.2463535532033698</v>
+        <v>-0.6971980796871855</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.002875916032281878</v>
+        <v>-0.06179828171208923</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.02679822357679484</v>
+        <v>-0.07585758999359726</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.1606551015610451</v>
+        <v>-0.1094380098131102</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1220948926797538</v>
+        <v>-0.3203837391909921</v>
       </c>
     </row>
     <row r="47">
@@ -5265,65 +5265,65 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>6.197694070468696</v>
+        <v>6.83910305526078</v>
       </c>
       <c r="C47" t="n">
-        <v>6.231552191893839</v>
+        <v>8.432807912734347</v>
       </c>
       <c r="D47" t="n">
-        <v>5.868422933907697</v>
+        <v>8.547446783408517</v>
       </c>
       <c r="E47" t="n">
-        <v>3.387278688932277</v>
+        <v>3.922916256022287</v>
       </c>
       <c r="F47" t="n">
-        <v>4.076746879128168</v>
+        <v>3.775552619678849</v>
       </c>
       <c r="G47" t="n">
-        <v>3.822061831790383</v>
+        <v>4.38787794130242</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8103839576431044</v>
+        <v>0.7606369112862693</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8083065464892191</v>
+        <v>0.6360821986023477</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8299965952239698</v>
+        <v>0.6261204636224402</v>
       </c>
       <c r="K47" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="L47" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M47" t="n">
         <v>0.7894736842105263</v>
       </c>
       <c r="N47" t="n">
-        <v>3.226659150038368</v>
+        <v>3.292789283556468</v>
       </c>
       <c r="O47" t="n">
-        <v>3.643781548832968</v>
+        <v>3.713746315164595</v>
       </c>
       <c r="P47" t="n">
-        <v>3.402323914546325</v>
+        <v>3.725335492636437</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5336,32 +5336,32 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W47" t="n">
-        <v>-0.03385812142514322</v>
+        <v>-1.593704857473567</v>
       </c>
       <c r="X47" t="n">
-        <v>0.3292711365609993</v>
+        <v>-1.708343728147738</v>
       </c>
       <c r="Y47" t="n">
-        <v>-0.6894681901958908</v>
+        <v>0.1473636363434383</v>
       </c>
       <c r="Z47" t="n">
-        <v>-0.4347831428581062</v>
+        <v>-0.4649616852801324</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.002077411153885378</v>
+        <v>-0.1245547126839216</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.0196126375808654</v>
+        <v>-0.1345164476638291</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.4171223987946</v>
+        <v>-0.4209570316081268</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1756647645079568</v>
+        <v>-0.4325462090799688</v>
       </c>
     </row>
     <row r="48">
@@ -5369,65 +5369,65 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>5.852291012760534</v>
+        <v>3.900857715031472</v>
       </c>
       <c r="C48" t="n">
-        <v>6.386218509720972</v>
+        <v>4.798234038250984</v>
       </c>
       <c r="D48" t="n">
-        <v>6.20021351282951</v>
+        <v>3.660914179163071</v>
       </c>
       <c r="E48" t="n">
-        <v>3.823382317537796</v>
+        <v>3.024419378012678</v>
       </c>
       <c r="F48" t="n">
-        <v>3.806088817335706</v>
+        <v>3.202711147597803</v>
       </c>
       <c r="G48" t="n">
-        <v>3.81115935225323</v>
+        <v>2.790923014206449</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8493896736005958</v>
+        <v>0.9342238213236178</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8206545056736209</v>
+        <v>0.9004797921156575</v>
       </c>
       <c r="J48" t="n">
-        <v>0.830949596157591</v>
+        <v>0.942066800228481</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="N48" t="n">
-        <v>3.058652832650469</v>
+        <v>2.869820735019897</v>
       </c>
       <c r="O48" t="n">
-        <v>3.061962506647209</v>
+        <v>3.049811901438332</v>
       </c>
       <c r="P48" t="n">
-        <v>3.077378055418757</v>
+        <v>2.713310133206667</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T48" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5440,32 +5440,32 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W48" t="n">
-        <v>-0.5339274969604375</v>
+        <v>-0.8973763232195116</v>
       </c>
       <c r="X48" t="n">
-        <v>-0.3479225000689761</v>
+        <v>0.239943535868401</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.01729350020208997</v>
+        <v>-0.1782917695851252</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.01222296528456601</v>
+        <v>0.2334963638062288</v>
       </c>
       <c r="AA48" t="n">
-        <v>-0.02873516792697495</v>
+        <v>-0.03374402920796027</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.0184400774430048</v>
+        <v>0.007842978904863185</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.003309673996739981</v>
+        <v>-0.1799911664184348</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.01872522276828814</v>
+        <v>0.1565106018132303</v>
       </c>
     </row>
     <row r="49">
@@ -5473,65 +5473,65 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>5.171954006305505</v>
+        <v>5.16593733168128</v>
       </c>
       <c r="C49" t="n">
-        <v>4.420507317608927</v>
+        <v>4.425033964570764</v>
       </c>
       <c r="D49" t="n">
-        <v>4.236830715250314</v>
+        <v>4.70475112050753</v>
       </c>
       <c r="E49" t="n">
-        <v>3.711936301027183</v>
+        <v>3.792179177049954</v>
       </c>
       <c r="F49" t="n">
-        <v>3.158907737476186</v>
+        <v>3.200547983056741</v>
       </c>
       <c r="G49" t="n">
-        <v>2.938056994681062</v>
+        <v>3.153508276359513</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8796283787795555</v>
+        <v>0.8714174905762166</v>
       </c>
       <c r="I49" t="n">
-        <v>0.912065554503051</v>
+        <v>0.9056554434736117</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9192212691588697</v>
+        <v>0.8933509627960694</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9210526315789473</v>
       </c>
       <c r="L49" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="N49" t="n">
-        <v>3.028770754564008</v>
+        <v>3.022481798793258</v>
       </c>
       <c r="O49" t="n">
-        <v>2.79626611389498</v>
+        <v>2.9665676877532</v>
       </c>
       <c r="P49" t="n">
-        <v>2.771426931553299</v>
+        <v>3.100215011296159</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T49" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5544,32 +5544,32 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W49" t="n">
-        <v>0.7514466886965776</v>
+        <v>0.7409033671105165</v>
       </c>
       <c r="X49" t="n">
-        <v>0.9351232910551905</v>
+        <v>0.4611862111737501</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.5530285635509968</v>
+        <v>0.5916311939932131</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.7738793063461209</v>
+        <v>0.6386709006904412</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.03243717572349558</v>
+        <v>0.03423795289739506</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.03959289037931424</v>
+        <v>0.02193347221985276</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.2325046406690281</v>
+        <v>0.05591411104005806</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.257343823010709</v>
+        <v>-0.07773321250290088</v>
       </c>
     </row>
     <row r="50">
@@ -5577,65 +5577,65 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>4.81539739056413</v>
+        <v>6.02415343428853</v>
       </c>
       <c r="C50" t="n">
-        <v>4.540528150839123</v>
+        <v>5.957737668214133</v>
       </c>
       <c r="D50" t="n">
-        <v>4.437434185157229</v>
+        <v>6.160944778745234</v>
       </c>
       <c r="E50" t="n">
-        <v>3.437060808852732</v>
+        <v>3.92347652518075</v>
       </c>
       <c r="F50" t="n">
-        <v>3.004101486935735</v>
+        <v>3.112993546113843</v>
       </c>
       <c r="G50" t="n">
-        <v>2.758587896033683</v>
+        <v>3.702464456880941</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8619210112154261</v>
+        <v>0.7910328244407904</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8772345735161969</v>
+        <v>0.7956151145130448</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8827461311941454</v>
+        <v>0.7814349806949478</v>
       </c>
       <c r="K50" t="n">
         <v>0.868421052631579</v>
       </c>
       <c r="L50" t="n">
-        <v>0.868421052631579</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="M50" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="N50" t="n">
-        <v>3.606810257471562</v>
+        <v>3.361638927546745</v>
       </c>
       <c r="O50" t="n">
-        <v>2.697054609906088</v>
+        <v>2.732849480209691</v>
       </c>
       <c r="P50" t="n">
-        <v>2.745716856625643</v>
+        <v>3.004065870505256</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T50" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5648,32 +5648,32 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W50" t="n">
-        <v>0.2748692397250077</v>
+        <v>0.06641576607439692</v>
       </c>
       <c r="X50" t="n">
-        <v>0.3779632054069015</v>
+        <v>-0.1367913444567046</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.4329593219169969</v>
+        <v>0.810482979066907</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.678472912819049</v>
+        <v>0.2210120682998089</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01531356230077086</v>
+        <v>0.004582290072254414</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.02082511997871928</v>
+        <v>-0.009597843745842605</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.9097556475654742</v>
+        <v>0.6287894473370539</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.861093400845919</v>
+        <v>0.3575730570414888</v>
       </c>
     </row>
     <row r="51">
@@ -5681,65 +5681,65 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>4.677253967009267</v>
+        <v>4.366574661775481</v>
       </c>
       <c r="C51" t="n">
-        <v>4.131692916527138</v>
+        <v>4.061485570724042</v>
       </c>
       <c r="D51" t="n">
-        <v>4.502766177679084</v>
+        <v>4.238382134676862</v>
       </c>
       <c r="E51" t="n">
-        <v>3.720128421666133</v>
+        <v>3.454391072202454</v>
       </c>
       <c r="F51" t="n">
-        <v>3.020071787226228</v>
+        <v>2.991269745991022</v>
       </c>
       <c r="G51" t="n">
-        <v>3.626982732747694</v>
+        <v>3.259315643485093</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8751525675704686</v>
+        <v>0.8988870806812747</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9025787309895869</v>
+        <v>0.9125228353381803</v>
       </c>
       <c r="J51" t="n">
-        <v>0.884293834396514</v>
+        <v>0.9047368167521844</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="L51" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="M51" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="N51" t="n">
-        <v>2.930119457037208</v>
+        <v>2.914292689524024</v>
       </c>
       <c r="O51" t="n">
-        <v>2.663703985567166</v>
+        <v>2.664091579945</v>
       </c>
       <c r="P51" t="n">
-        <v>2.899853188300672</v>
+        <v>2.857265295951201</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
+          <t>kernel=matern_1.5, restarts=0, alpha=1e-10</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
           <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>kernel=matern_1.5, restarts=0, alpha=0.01</t>
-        </is>
-      </c>
       <c r="T51" t="inlineStr">
         <is>
           <t>raw</t>
@@ -5752,32 +5752,32 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>kernel=rbf, restarts=0, alpha=1e-06</t>
+          <t>kernel=rbf, restarts=0, alpha=0.01</t>
         </is>
       </c>
       <c r="W51" t="n">
-        <v>0.5455610504821289</v>
+        <v>0.305089091051439</v>
       </c>
       <c r="X51" t="n">
-        <v>0.1744877893301826</v>
+        <v>0.1281925270986184</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.7000566344399051</v>
+        <v>0.4631213262114322</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.093145688918439</v>
+        <v>0.1950754287173608</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.0274261634191183</v>
+        <v>0.0136357546569057</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.009141266826045436</v>
+        <v>0.005849736070909772</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.266415471470042</v>
+        <v>0.2502011095790242</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.03026626873653582</v>
+        <v>0.05702739357282338</v>
       </c>
     </row>
   </sheetData>
